--- a/Montgomery_Fleet_Equipment_Inventory_FA_PART_2_START.xlsx
+++ b/Montgomery_Fleet_Equipment_Inventory_FA_PART_2_START.xlsx
@@ -1,29 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\stevesstuff\Job_Stuff\Skill-UpTechnologies\IBM\DataAnalystCurriculumDesign\Course 2 - Analyzing &amp; Visualizing Data Using Spreadsheets\Labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/47af7d917689c61e/Desktop/DATA ANALYTICS/Excel (Module 1)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{9011A403-47E5-440B-B7E1-02326158FD21}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09DF880D-85C7-459A-9F50-45E2DC7A0EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="7812" yWindow="0" windowWidth="15324" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Montgomery_Fleet_Equipment_Inve" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot Table 1" sheetId="4" r:id="rId2"/>
+    <sheet name="Pivot Table 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Pivot Table 3" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Montgomery_Fleet_Equipment_Inve!$A$1:$C$50</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId5"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="39">
   <si>
     <t>Department</t>
   </si>
@@ -110,13 +127,43 @@
   </si>
   <si>
     <t>Off Road Vehicle Equipment</t>
+  </si>
+  <si>
+    <t>Statistical Measure</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Equipment Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +298,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,8 +494,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -548,6 +616,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -593,8 +676,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="18" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="10" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="21" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -640,8 +735,22 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0066FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -651,6 +760,685 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="amjit" refreshedDate="46286.852829050928" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{628F95B9-2C99-4F7F-9F77-CE7EC6B19B2F}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="12">
+        <s v="Housing and Community Affairs"/>
+        <s v="Human Rights"/>
+        <s v="Libraries"/>
+        <s v="Liquor Control"/>
+        <s v="Office Of Homeland Security"/>
+        <s v="Permitting Services"/>
+        <s v="Public Information Office"/>
+        <s v="Recreation"/>
+        <s v="Sheriffs Office"/>
+        <s v="State Attorneys Office"/>
+        <s v="Technology Services"/>
+        <s v="Transportation"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Equipment Class" numFmtId="0">
+      <sharedItems count="14">
+        <s v="Pick Up Trucks"/>
+        <s v="SUV"/>
+        <s v="Sedan"/>
+        <s v="Van"/>
+        <s v="Medium Duty"/>
+        <s v="Heavy Duty"/>
+        <s v="CUV"/>
+        <s v="Off Road Vehicle Equipment"/>
+        <s v="Public Safety SUV"/>
+        <s v="Public Safety Van"/>
+        <s v="Public Safety CUV"/>
+        <s v="Public Safety Sedan"/>
+        <s v="Public Safety Pick Up Trucks"/>
+        <s v="Transit Bus"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Equipment Count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="379"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="49">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="23"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="42"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="9"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="10"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="11"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="12"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="11"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="93"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="248"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="13"/>
+    <n v="379"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="53"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="32"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="98"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="276"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="37"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64930102-469F-49E0-B5FA-A2628D2EF863}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E0EF479-81C4-4E81-901B-FEDCF5884DDA}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="22">
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{578C3D19-D0BE-4AB6-ABF5-07B7A0ABEE96}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="6"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D623A87E-BB02-4CC9-81E3-163CB4A16469}" name="Table1" displayName="Table1" ref="A1:C50" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C50" xr:uid="{D623A87E-BB02-4CC9-81E3-163CB4A16469}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EDAE4569-BFC5-45CB-A9F5-E568784E1906}" name="Department"/>
+    <tableColumn id="2" xr3:uid="{17BB5DF5-010E-48D1-88FC-9E788D5D5529}" name="Equipment Class"/>
+    <tableColumn id="3" xr3:uid="{6F02A49A-650A-45DD-8FF4-DC962FEBCD94}" name="Equipment Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -949,27 +1737,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -979,8 +1768,14 @@
       <c r="C2">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -990,8 +1785,15 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="4">
+        <f>SUM(Table1[Equipment Count])</f>
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1803,15 @@
       <c r="C4">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="4">
+        <f>AVERAGE(Table1[Equipment Count])</f>
+        <v>32.285714285714285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1012,8 +1821,15 @@
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4">
+        <f>MIN(Table1[Equipment Count])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1023,8 +1839,15 @@
       <c r="C6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4">
+        <f>MAX(Table1[Equipment Count])</f>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1034,8 +1857,15 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="4">
+        <f>COUNT(Table1[Equipment Count])</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1046,7 +1876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1057,7 +1887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1068,7 +1898,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1079,7 +1909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1090,7 +1920,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1101,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1112,7 +1942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1123,7 +1953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1145,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1156,7 +1986,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1167,7 +1997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1178,7 +2008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1189,7 +2019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1200,7 +2030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1211,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1222,7 +2052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1233,7 +2063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -1244,7 +2074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -1255,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -1266,7 +2096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1277,7 +2107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -1288,7 +2118,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -1299,7 +2129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1310,7 +2140,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -1321,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -1332,7 +2162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -1343,7 +2173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1354,7 +2184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1365,7 +2195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -1376,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -1387,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -1398,7 +2228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -1409,7 +2239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -1420,7 +2250,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -1431,7 +2261,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -1442,7 +2272,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -1453,7 +2283,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -1464,7 +2294,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -1475,7 +2305,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -1486,7 +2316,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -1497,7 +2327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -1506,6 +2336,499 @@
       </c>
       <c r="C50">
         <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038D2582-B739-4920-B8F2-3AC8B8231104}">
+  <dimension ref="A3:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1582</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E600F6-E9AF-4C41-AB63-12817F411CE3}">
+  <dimension ref="A3:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="7">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="7">
+        <v>1582</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27732A60-A6DA-4EE8-A3C5-832DBCAEBD39}">
+  <dimension ref="A3:B21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="7">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="7">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1582</v>
       </c>
     </row>
   </sheetData>

--- a/Montgomery_Fleet_Equipment_Inventory_FA_PART_2_START.xlsx
+++ b/Montgomery_Fleet_Equipment_Inventory_FA_PART_2_START.xlsx
@@ -1,29 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\stevesstuff\Job_Stuff\Skill-UpTechnologies\IBM\DataAnalystCurriculumDesign\Course 2 - Analyzing &amp; Visualizing Data Using Spreadsheets\Labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/47af7d917689c61e/Desktop/DATA ANALYTICS/Excel (Module 1)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{9011A403-47E5-440B-B7E1-02326158FD21}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09DF880D-85C7-459A-9F50-45E2DC7A0EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="48" yWindow="684" windowWidth="22992" windowHeight="11556" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Montgomery_Fleet_Equipment_Inve" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot Table 1" sheetId="4" r:id="rId2"/>
+    <sheet name="Pivot Table 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Pivot Table 3" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Montgomery_Fleet_Equipment_Inve!$A$1:$C$50</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId5"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="39">
   <si>
     <t>Department</t>
   </si>
@@ -110,13 +127,43 @@
   </si>
   <si>
     <t>Off Road Vehicle Equipment</t>
+  </si>
+  <si>
+    <t>Statistical Measure</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Equipment Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +298,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,8 +494,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -548,6 +616,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -593,8 +676,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="18" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="10" xfId="21" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="21" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -640,8 +734,22 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0066FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -651,6 +759,685 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="amjit" refreshedDate="46286.852829050928" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{628F95B9-2C99-4F7F-9F77-CE7EC6B19B2F}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="12">
+        <s v="Housing and Community Affairs"/>
+        <s v="Human Rights"/>
+        <s v="Libraries"/>
+        <s v="Liquor Control"/>
+        <s v="Office Of Homeland Security"/>
+        <s v="Permitting Services"/>
+        <s v="Public Information Office"/>
+        <s v="Recreation"/>
+        <s v="Sheriffs Office"/>
+        <s v="State Attorneys Office"/>
+        <s v="Technology Services"/>
+        <s v="Transportation"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Equipment Class" numFmtId="0">
+      <sharedItems count="14">
+        <s v="Pick Up Trucks"/>
+        <s v="SUV"/>
+        <s v="Sedan"/>
+        <s v="Van"/>
+        <s v="Medium Duty"/>
+        <s v="Heavy Duty"/>
+        <s v="CUV"/>
+        <s v="Off Road Vehicle Equipment"/>
+        <s v="Public Safety SUV"/>
+        <s v="Public Safety Van"/>
+        <s v="Public Safety CUV"/>
+        <s v="Public Safety Sedan"/>
+        <s v="Public Safety Pick Up Trucks"/>
+        <s v="Transit Bus"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Equipment Count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="379"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="49">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="23"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="42"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="9"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="27"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="24"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="9"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="10"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="11"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="12"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="11"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="11"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="93"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="248"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="13"/>
+    <n v="379"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="53"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="32"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="98"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="276"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="37"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64930102-469F-49E0-B5FA-A2628D2EF863}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E0EF479-81C4-4E81-901B-FEDCF5884DDA}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="22">
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{578C3D19-D0BE-4AB6-ABF5-07B7A0ABEE96}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="6"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Equipment Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D623A87E-BB02-4CC9-81E3-163CB4A16469}" name="Table1" displayName="Table1" ref="A1:C50" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:C50" xr:uid="{D623A87E-BB02-4CC9-81E3-163CB4A16469}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EDAE4569-BFC5-45CB-A9F5-E568784E1906}" name="Department"/>
+    <tableColumn id="2" xr3:uid="{17BB5DF5-010E-48D1-88FC-9E788D5D5529}" name="Equipment Class"/>
+    <tableColumn id="3" xr3:uid="{6F02A49A-650A-45DD-8FF4-DC962FEBCD94}" name="Equipment Count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -949,27 +1736,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -979,8 +1767,14 @@
       <c r="C2">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -990,8 +1784,15 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="4">
+        <f>SUM(Table1[Equipment Count])</f>
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1802,15 @@
       <c r="C4">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="4">
+        <f>AVERAGE(Table1[Equipment Count])</f>
+        <v>32.285714285714285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1012,8 +1820,15 @@
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4">
+        <f>MIN(Table1[Equipment Count])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1023,8 +1838,15 @@
       <c r="C6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4">
+        <f>MAX(Table1[Equipment Count])</f>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1034,8 +1856,15 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="4">
+        <f>COUNT(Table1[Equipment Count])</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1046,7 +1875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1057,7 +1886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1068,7 +1897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1079,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1090,7 +1919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1101,7 +1930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1112,7 +1941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1123,7 +1952,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1134,7 +1963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1145,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1156,7 +1985,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1167,7 +1996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1178,7 +2007,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1189,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1200,7 +2029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1211,7 +2040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -1222,7 +2051,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1233,7 +2062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -1244,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -1255,7 +2084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -1266,7 +2095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1277,7 +2106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -1288,7 +2117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -1299,7 +2128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1310,7 +2139,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -1321,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -1332,7 +2161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
@@ -1343,7 +2172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1354,7 +2183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>24</v>
       </c>
@@ -1365,7 +2194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -1376,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -1387,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -1398,7 +2227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -1409,7 +2238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -1420,7 +2249,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -1431,7 +2260,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -1442,7 +2271,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -1453,7 +2282,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -1464,7 +2293,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -1475,7 +2304,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -1486,7 +2315,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -1497,7 +2326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -1506,6 +2335,499 @@
       </c>
       <c r="C50">
         <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{038D2582-B739-4920-B8F2-3AC8B8231104}">
+  <dimension ref="A3:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>1582</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15E600F6-E9AF-4C41-AB63-12817F411CE3}">
+  <dimension ref="A3:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>1582</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27732A60-A6DA-4EE8-A3C5-832DBCAEBD39}">
+  <dimension ref="A3:B21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>1582</v>
       </c>
     </row>
   </sheetData>
